--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -8,15 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include ValueSet #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,12 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Jeu de valeurs permettant de coder l’agent responsable d’une allergie :
-- Médicaments : CIP ou UCD
-- Substances : SMS
-- Aliments : CIM-11 Chapitre X Extensions – Allergènes ou substances non médicinales
-- Agents environnementaux ou physiques : idem CIM-11 Chapitre X Extensions
-- Allergènes pouvant induire une contre-indication vaccinale : jdv-allergie-vaccin-cisis</t>
+    <t>Jeu de valeurs permettant de coder la substance responsable d’une allergie</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -116,19 +108,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-bdpm</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/terminologie-cip_ucd</t>
-  </si>
-  <si>
-    <t>http://id.who.int/icd/release/11/mms</t>
-  </si>
-  <si>
-    <t>ValueSet URL</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-allergie-vaccin-cisis</t>
+    <t>https://smt.esante.gouv.fr/terminologie-sms</t>
   </si>
 </sst>
 </file>
@@ -426,108 +406,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/main/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
